--- a/BBDD.xlsx
+++ b/BBDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/spino_duoc_cl/Documents/Clases/2026.1/GAA1903/Ev EXP 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83024D72-182F-4EAC-A265-55B3740145DC}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52FC9750-9632-47A9-9D4F-95AAF2384A95}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1785">
   <si>
     <t>2243</t>
   </si>
@@ -5308,9 +5308,6 @@
     <t>Juana Garrett</t>
   </si>
   <si>
-    <t>Barbara Fernandez</t>
-  </si>
-  <si>
     <t>Erica Rogers</t>
   </si>
   <si>
@@ -5396,6 +5393,12 @@
   </si>
   <si>
     <t>Kelly Guerrero</t>
+  </si>
+  <si>
+    <t>Bárbara Campos</t>
+  </si>
+  <si>
+    <t>masculino</t>
   </si>
 </sst>
 </file>
@@ -19658,10 +19661,10 @@
         <v>1036</v>
       </c>
       <c r="B12" t="s">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="C12" t="s">
-        <v>997</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -19779,7 +19782,7 @@
         <v>1025</v>
       </c>
       <c r="B23" t="s">
-        <v>1754</v>
+        <v>1783</v>
       </c>
       <c r="C23" t="s">
         <v>997</v>
@@ -19790,7 +19793,7 @@
         <v>1024</v>
       </c>
       <c r="B24" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="C24" t="s">
         <v>995</v>
@@ -19801,7 +19804,7 @@
         <v>1023</v>
       </c>
       <c r="B25" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="C25" t="s">
         <v>997</v>
@@ -19812,7 +19815,7 @@
         <v>1022</v>
       </c>
       <c r="B26" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C26" t="s">
         <v>995</v>
@@ -19823,7 +19826,7 @@
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="C27" t="s">
         <v>995</v>
@@ -19834,7 +19837,7 @@
         <v>396</v>
       </c>
       <c r="B28" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="C28" t="s">
         <v>995</v>
@@ -19845,7 +19848,7 @@
         <v>1020</v>
       </c>
       <c r="B29" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="C29" t="s">
         <v>995</v>
@@ -19856,7 +19859,7 @@
         <v>1019</v>
       </c>
       <c r="B30" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="C30" t="s">
         <v>995</v>
@@ -19867,7 +19870,7 @@
         <v>1018</v>
       </c>
       <c r="B31" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="C31" t="s">
         <v>995</v>
@@ -19878,7 +19881,7 @@
         <v>1017</v>
       </c>
       <c r="B32" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C32" t="s">
         <v>997</v>
@@ -19889,7 +19892,7 @@
         <v>1017</v>
       </c>
       <c r="B33" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C33" t="s">
         <v>997</v>
@@ -19900,7 +19903,7 @@
         <v>1017</v>
       </c>
       <c r="B34" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C34" t="s">
         <v>997</v>
@@ -19911,7 +19914,7 @@
         <v>1017</v>
       </c>
       <c r="B35" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C35" t="s">
         <v>997</v>
@@ -19922,7 +19925,7 @@
         <v>1017</v>
       </c>
       <c r="B36" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C36" t="s">
         <v>997</v>
@@ -19933,7 +19936,7 @@
         <v>1017</v>
       </c>
       <c r="B37" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C37" t="s">
         <v>997</v>
@@ -19944,7 +19947,7 @@
         <v>1017</v>
       </c>
       <c r="B38" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C38" t="s">
         <v>997</v>
@@ -19955,7 +19958,7 @@
         <v>1017</v>
       </c>
       <c r="B39" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C39" t="s">
         <v>997</v>
@@ -19966,7 +19969,7 @@
         <v>1017</v>
       </c>
       <c r="B40" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C40" t="s">
         <v>997</v>
@@ -19977,7 +19980,7 @@
         <v>1017</v>
       </c>
       <c r="B41" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C41" t="s">
         <v>997</v>
@@ -19988,7 +19991,7 @@
         <v>1017</v>
       </c>
       <c r="B42" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C42" t="s">
         <v>997</v>
@@ -19999,7 +20002,7 @@
         <v>1016</v>
       </c>
       <c r="B43" t="s">
-        <v>1764</v>
+        <v>1743</v>
       </c>
       <c r="C43" t="s">
         <v>997</v>
@@ -20010,7 +20013,7 @@
         <v>1015</v>
       </c>
       <c r="B44" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C44" t="s">
         <v>997</v>
@@ -20021,7 +20024,7 @@
         <v>1014</v>
       </c>
       <c r="B45" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C45" t="s">
         <v>997</v>
@@ -20032,7 +20035,7 @@
         <v>1013</v>
       </c>
       <c r="B46" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="C46" t="s">
         <v>997</v>
@@ -20043,7 +20046,7 @@
         <v>1012</v>
       </c>
       <c r="B47" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="C47" t="s">
         <v>997</v>
@@ -20054,7 +20057,7 @@
         <v>1011</v>
       </c>
       <c r="B48" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="C48" t="s">
         <v>997</v>
@@ -20065,7 +20068,7 @@
         <v>1010</v>
       </c>
       <c r="B49" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C49" t="s">
         <v>995</v>
@@ -20076,7 +20079,7 @@
         <v>1009</v>
       </c>
       <c r="B50" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C50" t="s">
         <v>997</v>
@@ -20087,7 +20090,7 @@
         <v>1008</v>
       </c>
       <c r="B51" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C51" t="s">
         <v>997</v>
@@ -20098,7 +20101,7 @@
         <v>1007</v>
       </c>
       <c r="B52" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C52" t="s">
         <v>995</v>
@@ -20109,7 +20112,7 @@
         <v>1006</v>
       </c>
       <c r="B53" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C53" t="s">
         <v>995</v>
@@ -20120,7 +20123,7 @@
         <v>1005</v>
       </c>
       <c r="B54" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C54" t="s">
         <v>997</v>
@@ -20131,7 +20134,7 @@
         <v>1004</v>
       </c>
       <c r="B55" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C55" t="s">
         <v>997</v>
@@ -20142,7 +20145,7 @@
         <v>1003</v>
       </c>
       <c r="B56" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C56" t="s">
         <v>995</v>
@@ -20153,7 +20156,7 @@
         <v>1002</v>
       </c>
       <c r="B57" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C57" t="s">
         <v>995</v>
@@ -20164,7 +20167,7 @@
         <v>1001</v>
       </c>
       <c r="B58" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C58" t="s">
         <v>997</v>
@@ -20175,7 +20178,7 @@
         <v>1000</v>
       </c>
       <c r="B59" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C59" t="s">
         <v>995</v>
@@ -20186,7 +20189,7 @@
         <v>999</v>
       </c>
       <c r="B60" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C60" t="s">
         <v>995</v>
@@ -20197,7 +20200,7 @@
         <v>998</v>
       </c>
       <c r="B61" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C61" t="s">
         <v>997</v>
@@ -20208,7 +20211,7 @@
         <v>996</v>
       </c>
       <c r="B62" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C62" t="s">
         <v>995</v>

--- a/BBDD.xlsx
+++ b/BBDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/spino_duoc_cl/Documents/Clases/2026.1/GAA1903/Ev EXP 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52FC9750-9632-47A9-9D4F-95AAF2384A95}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CF168E-ED48-4644-9F47-EB88EE47AAE2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="7" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Hoja3" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$3:$I$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja3!$A$2:$D$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3759" uniqueCount="1786">
   <si>
     <t>2243</t>
   </si>
@@ -5399,6 +5400,9 @@
   </si>
   <si>
     <t>masculino</t>
+  </si>
+  <si>
+    <t>31-</t>
   </si>
 </sst>
 </file>
@@ -6394,7 +6398,7 @@
         <v>50</v>
       </c>
       <c r="D30">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -6457,7 +6461,7 @@
         <v>56</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -6562,7 +6566,7 @@
         <v>66</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -7935,8 +7939,8 @@
       <c r="C124" t="s">
         <v>174</v>
       </c>
-      <c r="D124">
-        <v>10</v>
+      <c r="D124" t="s">
+        <v>1785</v>
       </c>
       <c r="E124">
         <v>14</v>
@@ -8315,8 +8319,8 @@
       <c r="C143" t="s">
         <v>208</v>
       </c>
-      <c r="D143">
-        <v>10</v>
+      <c r="D143" t="s">
+        <v>1785</v>
       </c>
       <c r="E143">
         <v>11</v>
@@ -9055,8 +9059,8 @@
       <c r="C180" t="s">
         <v>148</v>
       </c>
-      <c r="D180">
-        <v>10</v>
+      <c r="D180" t="s">
+        <v>1785</v>
       </c>
       <c r="E180">
         <v>5</v>
@@ -10615,8 +10619,8 @@
       <c r="C258" t="s">
         <v>379</v>
       </c>
-      <c r="D258">
-        <v>10</v>
+      <c r="D258" t="s">
+        <v>1785</v>
       </c>
       <c r="E258">
         <v>3</v>
@@ -10635,8 +10639,8 @@
       <c r="C259" t="s">
         <v>381</v>
       </c>
-      <c r="D259">
-        <v>10</v>
+      <c r="D259" t="s">
+        <v>1785</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -11155,8 +11159,8 @@
       <c r="C285" t="s">
         <v>233</v>
       </c>
-      <c r="D285">
-        <v>10</v>
+      <c r="D285" t="s">
+        <v>1785</v>
       </c>
       <c r="E285">
         <v>3</v>
@@ -11635,8 +11639,8 @@
       <c r="C309" t="s">
         <v>439</v>
       </c>
-      <c r="D309">
-        <v>10</v>
+      <c r="D309" t="s">
+        <v>1785</v>
       </c>
       <c r="E309">
         <v>18</v>
@@ -11735,8 +11739,8 @@
       <c r="C314" t="s">
         <v>447</v>
       </c>
-      <c r="D314">
-        <v>10</v>
+      <c r="D314" t="s">
+        <v>1785</v>
       </c>
       <c r="E314">
         <v>3</v>
@@ -13375,8 +13379,8 @@
       <c r="C396" t="s">
         <v>35</v>
       </c>
-      <c r="D396">
-        <v>10</v>
+      <c r="D396" t="s">
+        <v>1785</v>
       </c>
       <c r="E396">
         <v>3</v>
@@ -14115,8 +14119,8 @@
       <c r="C433" t="s">
         <v>565</v>
       </c>
-      <c r="D433">
-        <v>10</v>
+      <c r="D433" t="s">
+        <v>1785</v>
       </c>
       <c r="E433">
         <v>8</v>
@@ -16115,8 +16119,8 @@
       <c r="C533" t="s">
         <v>299</v>
       </c>
-      <c r="D533">
-        <v>10</v>
+      <c r="D533" t="s">
+        <v>1785</v>
       </c>
       <c r="E533">
         <v>21</v>
@@ -16655,8 +16659,8 @@
       <c r="C560" t="s">
         <v>601</v>
       </c>
-      <c r="D560">
-        <v>10</v>
+      <c r="D560" t="s">
+        <v>1785</v>
       </c>
       <c r="E560">
         <v>24</v>
@@ -16915,8 +16919,8 @@
       <c r="C573" t="s">
         <v>269</v>
       </c>
-      <c r="D573">
-        <v>10</v>
+      <c r="D573" t="s">
+        <v>1785</v>
       </c>
       <c r="E573">
         <v>16</v>
@@ -17795,8 +17799,8 @@
       <c r="C617" t="s">
         <v>673</v>
       </c>
-      <c r="D617">
-        <v>10</v>
+      <c r="D617" t="s">
+        <v>1785</v>
       </c>
       <c r="E617">
         <v>4</v>
@@ -19455,8 +19459,8 @@
       <c r="C700" t="s">
         <v>235</v>
       </c>
-      <c r="D700">
-        <v>10</v>
+      <c r="D700" t="s">
+        <v>1785</v>
       </c>
       <c r="E700">
         <v>2</v>
@@ -19526,6 +19530,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I39" xr:uid="{85791F65-41B5-48BF-BB08-9F382076A807}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/BBDD.xlsx
+++ b/BBDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/spino_duoc_cl/Documents/Clases/2026.1/GAA1903/Ev EXP 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CF168E-ED48-4644-9F47-EB88EE47AAE2}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27ACF79-1661-41E3-AE96-1DA54B8C97C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Hoja3" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$3:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$2:$F$703</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja3!$A$2:$D$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3759" uniqueCount="1786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1786">
   <si>
     <t>2243</t>
   </si>
@@ -5449,13 +5449,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
@@ -5802,21 +5801,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85791F65-41B5-48BF-BB08-9F382076A807}">
-  <dimension ref="A1:I703"/>
+  <dimension ref="A1:F703"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>1048</v>
       </c>
-      <c r="I1" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1732</v>
       </c>
@@ -5836,12 +5832,12 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1726</v>
       </c>
@@ -5860,9 +5856,8 @@
       <c r="F4" s="4">
         <v>44576</v>
       </c>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1725</v>
       </c>
@@ -5881,9 +5876,8 @@
       <c r="F5" s="4">
         <v>44585</v>
       </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1724</v>
       </c>
@@ -5902,9 +5896,8 @@
       <c r="F6" s="4">
         <v>44590</v>
       </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1723</v>
       </c>
@@ -5923,9 +5916,8 @@
       <c r="F7" s="4">
         <v>44577</v>
       </c>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1722</v>
       </c>
@@ -5944,9 +5936,8 @@
       <c r="F8" s="4">
         <v>44570</v>
       </c>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1721</v>
       </c>
@@ -5965,9 +5956,8 @@
       <c r="F9" s="4">
         <v>44566</v>
       </c>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1720</v>
       </c>
@@ -5986,9 +5976,8 @@
       <c r="F10" s="4">
         <v>44570</v>
       </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1719</v>
       </c>
@@ -6007,9 +5996,8 @@
       <c r="F11" s="4">
         <v>44588</v>
       </c>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1718</v>
       </c>
@@ -6028,9 +6016,8 @@
       <c r="F12" s="4">
         <v>44566</v>
       </c>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1717</v>
       </c>
@@ -6049,9 +6036,8 @@
       <c r="F13" s="4">
         <v>44578</v>
       </c>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1716</v>
       </c>
@@ -6070,9 +6056,8 @@
       <c r="F14" s="4">
         <v>44578</v>
       </c>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1715</v>
       </c>
@@ -6091,9 +6076,8 @@
       <c r="F15" s="4">
         <v>44569</v>
       </c>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1714</v>
       </c>
@@ -6104,7 +6088,7 @@
         <v>25</v>
       </c>
       <c r="D16">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -6112,9 +6096,8 @@
       <c r="F16" s="4">
         <v>44577</v>
       </c>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1713</v>
       </c>
@@ -6133,9 +6116,8 @@
       <c r="F17" s="4">
         <v>44588</v>
       </c>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1712</v>
       </c>
@@ -6154,9 +6136,8 @@
       <c r="F18" s="4">
         <v>44563</v>
       </c>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1711</v>
       </c>
@@ -6175,9 +6156,8 @@
       <c r="F19" s="4">
         <v>44567</v>
       </c>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1710</v>
       </c>
@@ -6196,9 +6176,8 @@
       <c r="F20" s="4">
         <v>44572</v>
       </c>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1709</v>
       </c>
@@ -6217,9 +6196,8 @@
       <c r="F21" s="4">
         <v>44585</v>
       </c>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1708</v>
       </c>
@@ -6238,9 +6216,8 @@
       <c r="F22" s="4">
         <v>44566</v>
       </c>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1707</v>
       </c>
@@ -6259,9 +6236,8 @@
       <c r="F23" s="4">
         <v>44566</v>
       </c>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1706</v>
       </c>
@@ -6280,9 +6256,8 @@
       <c r="F24" s="4">
         <v>44586</v>
       </c>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1705</v>
       </c>
@@ -6301,9 +6276,8 @@
       <c r="F25" s="4">
         <v>44576</v>
       </c>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1704</v>
       </c>
@@ -6322,9 +6296,8 @@
       <c r="F26" s="4">
         <v>44577</v>
       </c>
-      <c r="I26" s="5"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1703</v>
       </c>
@@ -6343,9 +6316,8 @@
       <c r="F27" s="4">
         <v>44564</v>
       </c>
-      <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1702</v>
       </c>
@@ -6364,9 +6336,8 @@
       <c r="F28" s="4">
         <v>44571</v>
       </c>
-      <c r="I28" s="5"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1701</v>
       </c>
@@ -6385,9 +6356,8 @@
       <c r="F29" s="4">
         <v>44581</v>
       </c>
-      <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1700</v>
       </c>
@@ -6406,9 +6376,8 @@
       <c r="F30" s="4">
         <v>44578</v>
       </c>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1699</v>
       </c>
@@ -6427,9 +6396,8 @@
       <c r="F31" s="4">
         <v>44571</v>
       </c>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1698</v>
       </c>
@@ -6448,9 +6416,8 @@
       <c r="F32" s="4">
         <v>44572</v>
       </c>
-      <c r="I32" s="5"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1697</v>
       </c>
@@ -6469,9 +6436,8 @@
       <c r="F33" s="4">
         <v>44566</v>
       </c>
-      <c r="I33" s="5"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1696</v>
       </c>
@@ -6490,9 +6456,8 @@
       <c r="F34" s="4">
         <v>44569</v>
       </c>
-      <c r="I34" s="5"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1695</v>
       </c>
@@ -6511,9 +6476,8 @@
       <c r="F35" s="4">
         <v>44582</v>
       </c>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1694</v>
       </c>
@@ -6532,9 +6496,8 @@
       <c r="F36" s="4">
         <v>44572</v>
       </c>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1693</v>
       </c>
@@ -6553,9 +6516,8 @@
       <c r="F37" s="4">
         <v>44592</v>
       </c>
-      <c r="I37" s="5"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1692</v>
       </c>
@@ -6574,9 +6536,8 @@
       <c r="F38" s="4">
         <v>44566</v>
       </c>
-      <c r="I38" s="5"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1691</v>
       </c>
@@ -6595,13 +6556,11 @@
       <c r="F39" s="4">
         <v>44585</v>
       </c>
-      <c r="I39" s="5"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F40" s="4"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1690</v>
       </c>
@@ -6620,9 +6579,8 @@
       <c r="F41" s="4">
         <v>44579</v>
       </c>
-      <c r="I41" s="5"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1689</v>
       </c>
@@ -6641,9 +6599,8 @@
       <c r="F42" s="4">
         <v>44587</v>
       </c>
-      <c r="I42" s="5"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1688</v>
       </c>
@@ -6662,9 +6619,8 @@
       <c r="F43" s="4">
         <v>44577</v>
       </c>
-      <c r="I43" s="5"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1687</v>
       </c>
@@ -6683,9 +6639,8 @@
       <c r="F44" s="4">
         <v>44576</v>
       </c>
-      <c r="I44" s="5"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1686</v>
       </c>
@@ -6704,9 +6659,8 @@
       <c r="F45" s="4">
         <v>44588</v>
       </c>
-      <c r="I45" s="5"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1685</v>
       </c>
@@ -6725,9 +6679,8 @@
       <c r="F46" s="4">
         <v>44567</v>
       </c>
-      <c r="I46" s="5"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1684</v>
       </c>
@@ -6746,9 +6699,8 @@
       <c r="F47" s="4">
         <v>44573</v>
       </c>
-      <c r="I47" s="5"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1683</v>
       </c>
@@ -6767,9 +6719,8 @@
       <c r="F48" s="4">
         <v>44567</v>
       </c>
-      <c r="I48" s="5"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1682</v>
       </c>
@@ -6788,9 +6739,8 @@
       <c r="F49" s="4">
         <v>44592</v>
       </c>
-      <c r="I49" s="5"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1681</v>
       </c>
@@ -6809,9 +6759,8 @@
       <c r="F50" s="4">
         <v>44572</v>
       </c>
-      <c r="I50" s="5"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1680</v>
       </c>
@@ -6830,9 +6779,8 @@
       <c r="F51" s="4">
         <v>44588</v>
       </c>
-      <c r="I51" s="5"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1679</v>
       </c>
@@ -6851,9 +6799,8 @@
       <c r="F52" s="4">
         <v>44581</v>
       </c>
-      <c r="I52" s="5"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1678</v>
       </c>
@@ -6872,9 +6819,8 @@
       <c r="F53" s="4">
         <v>44572</v>
       </c>
-      <c r="I53" s="5"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1677</v>
       </c>
@@ -6894,7 +6840,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1676</v>
       </c>
@@ -6914,7 +6860,7 @@
         <v>44613</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1675</v>
       </c>
@@ -6934,7 +6880,7 @@
         <v>44618</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1674</v>
       </c>
@@ -6954,7 +6900,7 @@
         <v>44598</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1673</v>
       </c>
@@ -6974,32 +6920,32 @@
         <v>44613</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F64" t="s">
         <v>1672</v>
       </c>
@@ -7280,7 +7226,7 @@
         <v>118</v>
       </c>
       <c r="D91">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E91">
         <v>12</v>
@@ -8300,7 +8246,7 @@
         <v>206</v>
       </c>
       <c r="D142">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E142">
         <v>6</v>
@@ -8400,7 +8346,7 @@
         <v>211</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E147">
         <v>9</v>
@@ -8520,7 +8466,7 @@
         <v>219</v>
       </c>
       <c r="D153">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E153">
         <v>18</v>
@@ -8780,7 +8726,7 @@
         <v>241</v>
       </c>
       <c r="D166">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E166">
         <v>15</v>
@@ -8800,7 +8746,7 @@
         <v>166</v>
       </c>
       <c r="D167">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E167">
         <v>11</v>
@@ -9300,7 +9246,7 @@
         <v>285</v>
       </c>
       <c r="D192">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E192">
         <v>7</v>
@@ -9600,7 +9546,7 @@
         <v>305</v>
       </c>
       <c r="D207">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E207">
         <v>4</v>
@@ -9940,7 +9886,7 @@
         <v>333</v>
       </c>
       <c r="D224">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E224">
         <v>15</v>
@@ -10420,7 +10366,7 @@
         <v>233</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E248">
         <v>20</v>
@@ -10840,7 +10786,7 @@
         <v>395</v>
       </c>
       <c r="D269">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E269">
         <v>27</v>
@@ -11340,7 +11286,7 @@
         <v>243</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E294">
         <v>19</v>
@@ -11920,7 +11866,7 @@
         <v>13</v>
       </c>
       <c r="D323">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E323">
         <v>17</v>
@@ -12580,7 +12526,7 @@
         <v>176</v>
       </c>
       <c r="D356">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E356">
         <v>22</v>
@@ -13160,7 +13106,7 @@
         <v>519</v>
       </c>
       <c r="D385">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E385">
         <v>9</v>
@@ -13620,7 +13566,7 @@
         <v>399</v>
       </c>
       <c r="D408">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E408">
         <v>12</v>
@@ -13760,7 +13706,7 @@
         <v>343</v>
       </c>
       <c r="D415">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E415">
         <v>13</v>
@@ -13780,7 +13726,7 @@
         <v>156</v>
       </c>
       <c r="D416">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E416">
         <v>19</v>
@@ -13900,7 +13846,7 @@
         <v>211</v>
       </c>
       <c r="D422">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E422">
         <v>4</v>
@@ -14740,7 +14686,7 @@
         <v>591</v>
       </c>
       <c r="D464">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E464">
         <v>9</v>
@@ -15180,7 +15126,7 @@
         <v>613</v>
       </c>
       <c r="D486">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E486">
         <v>5</v>
@@ -15280,7 +15226,7 @@
         <v>619</v>
       </c>
       <c r="D491">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E491">
         <v>13</v>
@@ -15420,7 +15366,7 @@
         <v>625</v>
       </c>
       <c r="D498">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E498">
         <v>9</v>
@@ -15600,7 +15546,7 @@
         <v>413</v>
       </c>
       <c r="D507">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E507">
         <v>2</v>
@@ -15760,7 +15706,7 @@
         <v>56</v>
       </c>
       <c r="D515">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E515">
         <v>8</v>
@@ -16200,7 +16146,7 @@
         <v>629</v>
       </c>
       <c r="D537">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E537">
         <v>13</v>
@@ -16300,7 +16246,7 @@
         <v>351</v>
       </c>
       <c r="D542">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E542">
         <v>12</v>
@@ -16620,7 +16566,7 @@
         <v>665</v>
       </c>
       <c r="D558">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E558">
         <v>28</v>
@@ -16860,7 +16806,7 @@
         <v>484</v>
       </c>
       <c r="D570">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E570">
         <v>19</v>
@@ -17140,7 +17086,7 @@
         <v>204</v>
       </c>
       <c r="D584">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E584">
         <v>28</v>
@@ -17160,7 +17106,7 @@
         <v>607</v>
       </c>
       <c r="D585">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E585">
         <v>2</v>
@@ -17440,7 +17386,7 @@
         <v>102</v>
       </c>
       <c r="D599">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E599">
         <v>17</v>
@@ -17620,7 +17566,7 @@
         <v>401</v>
       </c>
       <c r="D608">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E608">
         <v>19</v>
@@ -17880,7 +17826,7 @@
         <v>703</v>
       </c>
       <c r="D621">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E621">
         <v>23</v>
@@ -18160,7 +18106,7 @@
         <v>675</v>
       </c>
       <c r="D635">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E635">
         <v>3</v>
@@ -18340,7 +18286,7 @@
         <v>711</v>
       </c>
       <c r="D644">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E644">
         <v>21</v>
@@ -18940,7 +18886,7 @@
         <v>375</v>
       </c>
       <c r="D674">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E674">
         <v>1</v>
@@ -18980,7 +18926,7 @@
         <v>231</v>
       </c>
       <c r="D676">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E676">
         <v>6</v>
@@ -19530,7 +19476,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I39" xr:uid="{85791F65-41B5-48BF-BB08-9F382076A807}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19622,10 +19567,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>1739</v>
+        <v>1763</v>
       </c>
       <c r="C8" t="s">
-        <v>995</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -19666,10 +19611,10 @@
         <v>1036</v>
       </c>
       <c r="B12" t="s">
-        <v>1763</v>
+        <v>1743</v>
       </c>
       <c r="C12" t="s">
-        <v>1784</v>
+        <v>997</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -20007,10 +19952,10 @@
         <v>1016</v>
       </c>
       <c r="B43" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="C43" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">

--- a/BBDD.xlsx
+++ b/BBDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/spino_duoc_cl/Documents/Clases/2026.1/GAA1903/Ev EXP 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27ACF79-1661-41E3-AE96-1DA54B8C97C1}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{39FA1E83-AC02-46C7-BEF4-00F9457C3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A1F4B20-1047-4A3F-8399-2AB522A3F05C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EAE7B7B5-BC20-428E-BAA8-42107C28697D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="7" r:id="rId1"/>
@@ -19735,7 +19735,7 @@
         <v>1783</v>
       </c>
       <c r="C23" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
